--- a/data/trans_orig/IP07C11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>71562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86726</t>
+          <t>86689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>74170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>90716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150620</t>
+          <t>151343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173578</t>
+          <t>172862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34677</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>46411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>54883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76164</t>
+          <t>75322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87010</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109136</t>
+          <t>109698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107669</t>
+          <t>108128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128421</t>
+          <t>128895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203384</t>
+          <t>201111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231815</t>
+          <t>232649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60972</t>
+          <t>59965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>81638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47849</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>68555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115978</t>
+          <t>113919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143932</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163826</t>
+          <t>163944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190766</t>
+          <t>191355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187027</t>
+          <t>188840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>213376</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>361287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399259</t>
+          <t>398761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85997</t>
+          <t>84056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111720</t>
+          <t>112731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83593</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>107395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174038</t>
+          <t>174295</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210663</t>
+          <t>211281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95578</t>
+          <t>95701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113898</t>
+          <t>114059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91154</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110721</t>
+          <t>111055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194266</t>
+          <t>192996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220649</t>
+          <t>220604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39157</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76752</t>
+          <t>76609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103118</t>
+          <t>102950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13817</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84878</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105043</t>
+          <t>105028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102333</t>
+          <t>104321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123955</t>
+          <t>123695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194426</t>
+          <t>190614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223211</t>
+          <t>222142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71756</t>
+          <t>72558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40631</t>
+          <t>42086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98646</t>
+          <t>98858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126896</t>
+          <t>130760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185963</t>
+          <t>184454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>212799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200874</t>
+          <t>201709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>229545</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>396382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433429</t>
+          <t>434294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>90141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116282</t>
+          <t>117949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>86717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112466</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184366</t>
+          <t>181294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>220176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>28002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120238</t>
+          <t>121047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139741</t>
+          <t>141094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116093</t>
+          <t>116457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135987</t>
+          <t>135526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242533</t>
+          <t>242456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270569</t>
+          <t>272474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54288</t>
+          <t>53718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54430</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>74478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103033</t>
+          <t>103953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73309</t>
+          <t>72985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95642</t>
+          <t>96663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87846</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109316</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168989</t>
+          <t>168514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199483</t>
+          <t>199837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73375</t>
+          <t>74087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113726</t>
+          <t>112721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142648</t>
+          <t>143890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31115</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198021</t>
+          <t>199921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229982</t>
+          <t>231024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209830</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239751</t>
+          <t>241555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>419028</t>
+          <t>417892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461240</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>94567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124017</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196382</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237216</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C11-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82805</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73786</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>91038</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>79659</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>71562</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86689</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72114</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>86632</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>82805</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>74170</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>90716</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>67,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151343</t>
+          <t>151611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172862</t>
+          <t>174472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38156</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30279</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47552</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26738</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19451</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19876</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34120</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38156</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30285</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46411</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>75446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2519</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6651</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6146</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2693</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6730</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6252</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>118596</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107036</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>128142</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>98760</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88388</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>109698</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88711</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>110001</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>118596</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>108128</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128895</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201111</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232649</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57742</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48616</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68602</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70924</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59965</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81638</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60863</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>81284</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57742</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47428</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68555</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113919</t>
+          <t>114964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144742</t>
+          <t>142973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -1635,67 +1635,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16021</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>9251</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5251</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15085</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>14276</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9759</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15485</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>201401</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187307</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>215193</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>178419</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>163944</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>191355</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>164984</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190548</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>201401</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>188840</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>214901</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>361287</t>
+          <t>361010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>398761</t>
+          <t>399290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>95899</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81845</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>108829</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>97663</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>84056</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112731</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>86188</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>110904</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>95899</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>83714</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>107395</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>174295</t>
+          <t>175400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211281</t>
+          <t>211890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>12278</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7583</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18743</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>11871</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7267</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18828</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7158</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17978</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12278</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7637</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19343</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2693</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6709</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101425</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91882</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>111540</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>105467</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>95701</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114059</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>96197</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>113816</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>101425</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>91718</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>111055</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>193691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220604</t>
+          <t>220922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,34%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48381</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41168</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33161</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50459</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33323</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>50744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48381</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38608</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58273</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76609</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102950</t>
+          <t>101962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5621</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2420</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2721</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6558</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5621</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2796</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10985</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3972</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>113521</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>102896</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122761</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>94404</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83653</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105028</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>83498</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104029</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>58,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>113521</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>104321</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>123695</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190614</t>
+          <t>194086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222142</t>
+          <t>221269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41610</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61485</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62114</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>51278</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72558</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52168</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72299</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51100</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>42086</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>61422</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98858</t>
+          <t>98945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130760</t>
+          <t>127182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -3911,67 +3911,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>5450</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10072</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>5690</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2482</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5450</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10437</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4019,107 +4019,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>214946</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>200528</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>228504</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>199871</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>184454</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>212799</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>184623</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>214475</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>214946</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>201709</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>228517</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396382</t>
+          <t>393849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434294</t>
+          <t>434326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>99481</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>103282</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>90141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117949</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>90072</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>118549</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>99481</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>86717</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112985</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>184648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>220176</t>
+          <t>224352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11071</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17418</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14264</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>14338</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11071</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6455</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17524</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4706,102 +4706,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1189</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4221</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>312174</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la menor en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>126225</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>115130</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>135584</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>130746</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>121047</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>141094</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>119849</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>139568</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>72,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>126225</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>116457</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>135526</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242456</t>
+          <t>242723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>271836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45399</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36365</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56052</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44055</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>34185</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53718</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34880</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55008</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>45399</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36786</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55267</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74478</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>103874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11025</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4860</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9062</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9997</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6228</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11927</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5618,102 +5618,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3057</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4780</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180225</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180225</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180225</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99568</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88999</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110480</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>84434</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72985</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96663</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73077</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94877</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>99568</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87974</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>109833</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168514</t>
+          <t>167363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199837</t>
+          <t>198418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63177</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53696</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73867</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64014</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52439</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73950</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53777</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74936</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63177</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51978</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74087</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112721</t>
+          <t>112986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143890</t>
+          <t>144008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7846</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4168</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13404</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14949</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22370</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10194</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21782</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,07%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7846</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4167</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13412</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>225793</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>209981</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>240816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>215180</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>199921</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>231024</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>201611</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>231219</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>225793</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>209938</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>241555</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>417892</t>
+          <t>419518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>460562</t>
+          <t>462181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>108576</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>93579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>124195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>108069</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93947</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122777</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>91762</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121233</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>108576</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>94567</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>124415</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197385</t>
+          <t>195624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238737</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14074</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20503</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19809</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13411</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>27143</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14156</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>28208</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>14074</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>21082</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>45412</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1356</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7090,107 +7090,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3663</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345032</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345032</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345032</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
